--- a/data/trans_dic/P04D$notiene-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P04D$notiene-Clase-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no tiene calefacción ni aparatos de calefacción en su vivienda</t>
+          <t>Población que no tiene calefacción ni aparatos de calefacción en su vivienda (tasa de respuesta: 99,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,61; 7,0</t>
+          <t>2,5; 7,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,25; 13,67</t>
+          <t>7,35; 13,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,19; 11,45</t>
+          <t>6,24; 11,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,66; 6,87</t>
+          <t>1,63; 7,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,61; 13,23</t>
+          <t>6,8; 13,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,74; 15,0</t>
+          <t>8,79; 14,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,67; 6,18</t>
+          <t>2,7; 5,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,7; 12,43</t>
+          <t>7,85; 12,35</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,06; 11,79</t>
+          <t>8,18; 12,18</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,92; 4,19</t>
+          <t>0,87; 3,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,71; 14,46</t>
+          <t>7,66; 14,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,17; 14,6</t>
+          <t>8,17; 14,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,0; 7,84</t>
+          <t>2,97; 7,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,7; 13,2</t>
+          <t>6,63; 12,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,08; 16,19</t>
+          <t>9,96; 16,51</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,16; 4,82</t>
+          <t>2,17; 4,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,85; 12,59</t>
+          <t>7,96; 12,53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,88; 14,32</t>
+          <t>9,93; 14,34</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,52; 5,8</t>
+          <t>2,48; 5,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,05; 18,35</t>
+          <t>11,87; 18,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,89; 11,13</t>
+          <t>2,17; 11,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,42; 9,2</t>
+          <t>3,16; 8,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,69; 14,7</t>
+          <t>4,87; 13,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,41; 18,57</t>
+          <t>9,19; 18,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,24; 6,07</t>
+          <t>3,2; 5,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,17; 16,67</t>
+          <t>10,73; 16,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,2; 11,9</t>
+          <t>2,62; 11,88</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,48; 6,0</t>
+          <t>3,54; 5,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,42; 18,8</t>
+          <t>14,16; 18,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,75; 14,8</t>
+          <t>9,62; 14,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,19; 6,55</t>
+          <t>3,22; 6,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,86; 17,98</t>
+          <t>13,06; 17,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,59; 12,31</t>
+          <t>4,55; 12,37</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,76; 5,83</t>
+          <t>3,77; 5,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,33; 17,79</t>
+          <t>14,29; 17,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,42; 12,54</t>
+          <t>7,42; 12,56</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,16; 6,9</t>
+          <t>3,04; 7,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,83; 24,59</t>
+          <t>18,12; 24,8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,56; 16,53</t>
+          <t>10,32; 16,92</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,62; 5,58</t>
+          <t>2,68; 5,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,78; 20,41</t>
+          <t>14,64; 20,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,44; 42,51</t>
+          <t>9,23; 38,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,36; 5,71</t>
+          <t>3,18; 5,64</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>17,19; 21,59</t>
+          <t>17,02; 21,61</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10,65; 31,13</t>
+          <t>10,67; 29,67</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,16; 7,66</t>
+          <t>1,87; 7,37</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12,12; 20,8</t>
+          <t>12,24; 20,71</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,32; 20,91</t>
+          <t>4,77; 19,79</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,39; 5,97</t>
+          <t>3,41; 6,09</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>14,2; 19,04</t>
+          <t>13,79; 18,88</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,32; 13,05</t>
+          <t>8,26; 12,61</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,44; 5,65</t>
+          <t>3,42; 5,68</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14,26; 18,42</t>
+          <t>14,5; 18,52</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8,14; 13,29</t>
+          <t>8,2; 12,97</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,49; 4,92</t>
+          <t>3,48; 4,9</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>14,36; 17,04</t>
+          <t>14,36; 16,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,9; 11,75</t>
+          <t>7,9; 11,86</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,84; 5,28</t>
+          <t>3,81; 5,29</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>13,47; 15,89</t>
+          <t>13,42; 15,85</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,91; 18,84</t>
+          <t>9,86; 19,04</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,85; 4,81</t>
+          <t>3,85; 4,9</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>14,19; 15,96</t>
+          <t>14,23; 16,03</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,77; 14,53</t>
+          <t>9,62; 14,09</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no tiene calefacción ni aparatos de calefacción en su vivienda</t>
+          <t>Población que no tiene calefacción ni aparatos de calefacción en su vivienda (tasa de respuesta: 99,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11424; 30622</t>
+          <t>10946; 32041</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>31095; 58650</t>
+          <t>31532; 57933</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31215; 57747</t>
+          <t>31464; 57430</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5213; 21589</t>
+          <t>5125; 23036</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>22932; 45922</t>
+          <t>23615; 46486</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>39002; 66924</t>
+          <t>39225; 64425</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20085; 46421</t>
+          <t>20276; 44749</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>59763; 96480</t>
+          <t>60918; 95881</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>76589; 112020</t>
+          <t>77712; 115766</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3826; 17461</t>
+          <t>3621; 16561</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29085; 54539</t>
+          <t>28897; 54034</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36963; 66041</t>
+          <t>36949; 66596</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10135; 26488</t>
+          <t>10030; 26642</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24941; 49158</t>
+          <t>24671; 46270</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>38559; 61953</t>
+          <t>38118; 63158</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16277; 36338</t>
+          <t>16347; 36784</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>58869; 94364</t>
+          <t>59662; 93903</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>82500; 119583</t>
+          <t>82922; 119699</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>15867; 36501</t>
+          <t>15605; 36453</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>62901; 95786</t>
+          <t>61948; 95650</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12582; 74292</t>
+          <t>14500; 73649</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8901; 23925</t>
+          <t>8223; 22972</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7796; 24418</t>
+          <t>8096; 22963</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15545; 30680</t>
+          <t>15188; 31083</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28817; 54002</t>
+          <t>28460; 52941</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>76820; 114677</t>
+          <t>73813; 112529</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>26655; 99072</t>
+          <t>21812; 98911</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>40219; 69434</t>
+          <t>40916; 69278</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>165749; 216110</t>
+          <t>162825; 216215</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>100599; 152668</t>
+          <t>99304; 151125</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>24409; 50150</t>
+          <t>24671; 52096</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>106219; 148497</t>
+          <t>107843; 147801</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>44793; 120267</t>
+          <t>44476; 120861</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>72373; 112009</t>
+          <t>72413; 111248</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>283068; 351474</t>
+          <t>282206; 348972</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>148955; 251949</t>
+          <t>148942; 252191</t>
         </is>
       </c>
     </row>
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>16065; 35119</t>
+          <t>15483; 36373</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>110699; 152629</t>
+          <t>112444; 153939</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>50060; 78340</t>
+          <t>48940; 80207</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>19930; 42393</t>
+          <t>20369; 44680</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>109135; 150697</t>
+          <t>108100; 152385</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>79240; 356816</t>
+          <t>77515; 326272</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>42680; 72451</t>
+          <t>40353; 71547</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>233659; 293407</t>
+          <t>231252; 293705</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>139931; 408882</t>
+          <t>140148; 389732</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5752; 20366</t>
+          <t>4970; 19607</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>34813; 59740</t>
+          <t>35145; 59473</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12793; 50288</t>
+          <t>11470; 47585</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>37529; 66057</t>
+          <t>37775; 67446</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>153688; 206020</t>
+          <t>149233; 204334</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>63185; 99141</t>
+          <t>62787; 95790</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>47238; 77589</t>
+          <t>46954; 77952</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>195286; 252198</t>
+          <t>198539; 253560</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>81428; 132963</t>
+          <t>82065; 129773</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>119145; 168057</t>
+          <t>118858; 167453</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>486038; 576785</t>
+          <t>486029; 570879</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>266203; 396028</t>
+          <t>266319; 399716</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>136213; 187076</t>
+          <t>135024; 187717</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>475688; 561346</t>
+          <t>473840; 559848</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>353643; 672730</t>
+          <t>351857; 679644</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>268148; 335081</t>
+          <t>268063; 341391</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>981727; 1104254</t>
+          <t>984070; 1108861</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>677779; 1008507</t>
+          <t>667398; 978106</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P04D$notiene-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P04D$notiene-Clase-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>10,93%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,5; 7,33</t>
+          <t>2,57; 7,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,35; 13,5</t>
+          <t>7,36; 13,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,24; 11,39</t>
+          <t>7,4; 12,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,63; 7,33</t>
+          <t>1,62; 6,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,8; 13,39</t>
+          <t>6,74; 13,3</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,79; 14,44</t>
+          <t>9,65; 15,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,7; 5,95</t>
+          <t>2,72; 6,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,85; 12,35</t>
+          <t>7,93; 12,13</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,18; 12,18</t>
+          <t>9,13; 13,11</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,27%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,87; 3,98</t>
+          <t>0,91; 4,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,66; 14,32</t>
+          <t>7,85; 14,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,17; 14,73</t>
+          <t>8,62; 15,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,97; 7,88</t>
+          <t>2,84; 7,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,63; 12,43</t>
+          <t>6,51; 12,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,96; 16,51</t>
+          <t>10,46; 16,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,17; 4,88</t>
+          <t>2,13; 4,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,96; 12,53</t>
+          <t>8,03; 12,72</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,93; 14,34</t>
+          <t>10,3; 14,66</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>11,51%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,48; 5,79</t>
+          <t>2,49; 6,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,87; 18,33</t>
+          <t>11,87; 18,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,17; 11,04</t>
+          <t>7,71; 13,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,16; 8,83</t>
+          <t>3,42; 9,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,87; 13,82</t>
+          <t>4,83; 14,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,19; 18,81</t>
+          <t>10,76; 20,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,2; 5,95</t>
+          <t>3,08; 5,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,73; 16,36</t>
+          <t>10,99; 16,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,62; 11,88</t>
+          <t>9,38; 14,52</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>12,91%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,54; 5,99</t>
+          <t>3,52; 6,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,16; 18,81</t>
+          <t>14,25; 18,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,62; 14,65</t>
+          <t>10,78; 15,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,22; 6,8</t>
+          <t>3,33; 6,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,06; 17,9</t>
+          <t>13,09; 18,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,55; 12,37</t>
+          <t>11,28; 15,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,77; 5,79</t>
+          <t>3,81; 5,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,29; 17,66</t>
+          <t>14,26; 17,78</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,42; 12,56</t>
+          <t>11,36; 14,4</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>13,92%</t>
         </is>
       </c>
     </row>
@@ -1118,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,04; 7,15</t>
+          <t>3,16; 7,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18,12; 24,8</t>
+          <t>18,25; 24,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,32; 16,92</t>
+          <t>13,97; 20,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,68; 5,88</t>
+          <t>2,78; 5,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,64; 20,64</t>
+          <t>14,88; 20,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,23; 38,87</t>
+          <t>10,0; 13,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,18; 5,64</t>
+          <t>3,32; 5,66</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>17,02; 21,61</t>
+          <t>17,07; 21,36</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10,67; 29,67</t>
+          <t>12,1; 15,99</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,49%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,87; 7,37</t>
+          <t>2,16; 7,8</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12,24; 20,71</t>
+          <t>12,06; 20,82</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,77; 19,79</t>
+          <t>4,67; 19,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,41; 6,09</t>
+          <t>3,29; 5,89</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13,79; 18,88</t>
+          <t>14,35; 18,89</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,26; 12,61</t>
+          <t>8,79; 12,85</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,42; 5,68</t>
+          <t>3,37; 5,66</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14,5; 18,52</t>
+          <t>14,35; 18,48</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8,2; 12,97</t>
+          <t>8,54; 12,88</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>12,24%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,48; 4,9</t>
+          <t>3,43; 4,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>14,36; 16,86</t>
+          <t>14,39; 16,95</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,9; 11,86</t>
+          <t>11,09; 13,71</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,81; 5,29</t>
+          <t>3,85; 5,21</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>13,42; 15,85</t>
+          <t>13,43; 15,9</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,86; 19,04</t>
+          <t>11,3; 13,33</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,85; 4,9</t>
+          <t>3,84; 4,84</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>14,23; 16,03</t>
+          <t>14,17; 15,94</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,62; 14,09</t>
+          <t>11,53; 13,17</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43103</t>
+          <t>53468</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49973</t>
+          <t>59775</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>93076</t>
+          <t>113244</t>
         </is>
       </c>
     </row>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10946; 32041</t>
+          <t>11241; 31150</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>31532; 57933</t>
+          <t>31598; 59170</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31464; 57430</t>
+          <t>40670; 70436</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5125; 23036</t>
+          <t>5105; 21714</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>23615; 46486</t>
+          <t>23386; 46149</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>39225; 64425</t>
+          <t>46981; 75016</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20276; 44749</t>
+          <t>20480; 48017</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>60918; 95881</t>
+          <t>61566; 94136</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>77712; 115766</t>
+          <t>94589; 135886</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>50286</t>
+          <t>55435</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>49846</t>
+          <t>55788</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>100132</t>
+          <t>111223</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3621; 16561</t>
+          <t>3786; 17327</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>28897; 54034</t>
+          <t>29607; 54951</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36949; 66596</t>
+          <t>41656; 72528</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10030; 26642</t>
+          <t>9610; 26895</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24671; 46270</t>
+          <t>24246; 46967</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>38118; 63158</t>
+          <t>44252; 68976</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16347; 36784</t>
+          <t>16047; 36625</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>59662; 93903</t>
+          <t>60199; 95323</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>82922; 119699</t>
+          <t>93394; 132887</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>42894</t>
+          <t>48685</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22171</t>
+          <t>26890</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>65065</t>
+          <t>75575</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>15605; 36453</t>
+          <t>15665; 37975</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>61948; 95650</t>
+          <t>61932; 96531</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14500; 73649</t>
+          <t>36270; 63411</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8223; 22972</t>
+          <t>8894; 24036</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8096; 22963</t>
+          <t>8016; 23334</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15188; 31083</t>
+          <t>19986; 37561</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28460; 52941</t>
+          <t>27413; 53028</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>73813; 112529</t>
+          <t>75629; 114438</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>21812; 98911</t>
+          <t>61602; 95322</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>123577</t>
+          <t>142499</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89999</t>
+          <t>113731</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>213576</t>
+          <t>256230</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>40916; 69278</t>
+          <t>40772; 70499</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>162825; 216215</t>
+          <t>163803; 216619</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>99304; 151125</t>
+          <t>121276; 171323</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>24671; 52096</t>
+          <t>25507; 51153</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>107843; 147801</t>
+          <t>108103; 149046</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>44476; 120861</t>
+          <t>96869; 130499</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>72413; 111248</t>
+          <t>73328; 112543</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>282206; 348972</t>
+          <t>281802; 351339</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>148942; 252191</t>
+          <t>225509; 285760</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>62822</t>
+          <t>97552</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>146526</t>
+          <t>96767</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>209348</t>
+          <t>194319</t>
         </is>
       </c>
     </row>
@@ -2291,54 +2291,54 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>15483; 36373</t>
+          <t>16066; 35819</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>112444; 153939</t>
+          <t>113308; 154811</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>48940; 80207</t>
+          <t>79192; 118031</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>20369; 44680</t>
+          <t>21103; 44258</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>108100; 152385</t>
+          <t>109882; 152525</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>77515; 326272</t>
+          <t>82881; 113894</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>40353; 71547</t>
+          <t>42098; 71841</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>231252; 293705</t>
+          <t>232003; 290314</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>140148; 389732</t>
+          <t>168856; 223166</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>25647</t>
+          <t>23721</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76916</t>
+          <t>89492</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>102562</t>
+          <t>113213</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4970; 19607</t>
+          <t>5753; 20740</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>35145; 59473</t>
+          <t>34631; 59779</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11470; 47585</t>
+          <t>11075; 45067</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>37775; 67446</t>
+          <t>36380; 65179</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>149233; 204334</t>
+          <t>155275; 204408</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>62787; 95790</t>
+          <t>74029; 108256</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>46954; 77952</t>
+          <t>46231; 77785</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>198539; 253560</t>
+          <t>196533; 253046</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>82065; 129773</t>
+          <t>92223; 139045</t>
         </is>
       </c>
     </row>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>348329</t>
+          <t>421360</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>435431</t>
+          <t>442443</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>783760</t>
+          <t>863804</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>118858; 167453</t>
+          <t>117114; 168671</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>486029; 570879</t>
+          <t>487038; 573918</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>266319; 399716</t>
+          <t>380745; 470540</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>135024; 187717</t>
+          <t>136634; 184753</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>473840; 559848</t>
+          <t>474288; 561646</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>351857; 679644</t>
+          <t>409602; 483304</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>268063; 341391</t>
+          <t>267403; 336973</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>984070; 1108861</t>
+          <t>980261; 1102442</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>667398; 978106</t>
+          <t>813983; 929725</t>
         </is>
       </c>
     </row>
